--- a/EXCEL/class notes/day1&2 basics/First day Basic class.xlsx
+++ b/EXCEL/class notes/day1&2 basics/First day Basic class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day1&amp;2 basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CC34D0-2AF3-4A1F-953D-1B99191F6DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3785AB96-F699-4744-9BFD-FDB9B17E7C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{DA7DA723-D9E6-4E34-93FE-A312ACA73533}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{DA7DA723-D9E6-4E34-93FE-A312ACA73533}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic information" sheetId="3" r:id="rId1"/>
@@ -24,12 +24,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
   <si>
     <t>abc</t>
   </si>
@@ -345,12 +354,21 @@
       <t>charter, Special charter, alfa numric</t>
     </r>
   </si>
+  <si>
+    <t>alt enter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>autofit column width</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,8 +412,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,8 +469,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -764,11 +795,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -790,7 +832,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -821,9 +862,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
@@ -871,12 +909,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
@@ -884,11 +917,162 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1259,11 +1443,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D5F36D1-A3DD-4EAB-825B-1F82B19E22BD}" name="Table1" displayName="Table1" ref="H4:J15" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFF9B276-CD00-4808-95E3-220A51FA6F92}" name="Table2" displayName="Table2" ref="A5:C16" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+  <autoFilter ref="A5:C16" xr:uid="{EFF9B276-CD00-4808-95E3-220A51FA6F92}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{6E40DE32-A0A6-45ED-9371-D43E3EF12F08}" name="ID" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{661F6492-0360-4E30-B030-106AC1E3EA6D}" name="Name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{9053E576-F820-4739-BBF4-C729158BD5FE}" name="Mark" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D5F36D1-A3DD-4EAB-825B-1F82B19E22BD}" name="Table1" displayName="Table1" ref="H4:J15" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="H4:J15" xr:uid="{2D5F36D1-A3DD-4EAB-825B-1F82B19E22BD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F1551E8F-DF99-43C6-B1A3-F48CE83197D7}" name="ID" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{250F4033-04AD-4E23-BBA6-16DCE80D3841}" name="Name" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F1551E8F-DF99-43C6-B1A3-F48CE83197D7}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{250F4033-04AD-4E23-BBA6-16DCE80D3841}" name="Name" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{1632EAEB-30BF-4107-85EB-FD12E9B1EA9B}" name="Mark"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1567,43 +1763,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD05C59-D740-4FA8-ABA7-B5889F88C29B}">
-  <dimension ref="A2:P18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:T18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E2" s="1">
         <v>123</v>
       </c>
-      <c r="O2" s="74" t="s">
+      <c r="O2" s="67" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="O3" s="74" t="s">
+      <c r="O3" s="67" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E4" s="12"/>
       <c r="G4" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="34" t="s">
+      <c r="O4" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="71" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1621,28 +1834,28 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="13">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
         <v>1001</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="24">
         <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="21">
         <v>1002</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="25">
         <v>35</v>
       </c>
       <c r="E7" s="12"/>
@@ -1650,14 +1863,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
         <v>1003</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="24">
         <v>16</v>
       </c>
       <c r="E8" s="4">
@@ -1679,14 +1892,14 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="16">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
         <v>1004</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="23">
         <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1702,14 +1915,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
         <v>1005</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="24">
         <v>53</v>
       </c>
       <c r="E10" s="1">
@@ -1728,14 +1941,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="68">
         <v>1006</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="24">
         <v>95</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1757,14 +1970,14 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
         <v>1007</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="24">
         <v>57</v>
       </c>
       <c r="E12" s="1">
@@ -1780,14 +1993,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
         <v>1008</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="24">
         <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1806,14 +2019,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="16">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
         <v>1009</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="23">
         <v>82</v>
       </c>
       <c r="H14" s="5" t="s">
@@ -1832,14 +2045,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
         <v>1010</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="22">
         <v>38</v>
       </c>
       <c r="N15" s="9">
@@ -1852,14 +2065,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="72">
         <v>1011</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="74">
         <v>53</v>
       </c>
       <c r="G16" s="12" t="s">
@@ -1875,28 +2088,28 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H17" s="5" t="s">
+    <row r="17" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="L17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="N17" s="9">
+      <c r="R17" s="9">
         <v>1009</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="S17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="P17" s="9">
+      <c r="T17" s="9">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="N18" s="9">
+    <row r="18" spans="12:20" x14ac:dyDescent="0.3">
+      <c r="R18" s="9">
         <v>1010</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="S18" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="P18" s="9">
+      <c r="T18" s="9">
         <v>17</v>
       </c>
     </row>
@@ -1905,23 +2118,26 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425DFA22-1E76-408A-8CDB-133DC835E696}">
-  <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>CHAR(65)</f>
         <v>A</v>
@@ -1933,12 +2149,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="C3" s="33" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C3" s="32" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C4" s="6">
         <v>1</v>
       </c>
@@ -1949,7 +2165,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>65</v>
       </c>
@@ -1974,7 +2190,7 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C6" s="6">
         <v>123</v>
       </c>
@@ -1982,7 +2198,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="str">
         <f>DEC2BIN(A5)</f>
         <v>1000001</v>
@@ -2000,7 +2216,7 @@
         <f>COUNTA(C3:C16)</f>
         <v>11</v>
       </c>
-      <c r="J7" s="57">
+      <c r="J7" s="55">
         <f>I7-I5</f>
         <v>6</v>
       </c>
@@ -2008,7 +2224,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>1</v>
       </c>
@@ -2016,7 +2232,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" s="6" t="s">
         <v>2</v>
       </c>
@@ -2034,7 +2250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C10" s="6">
         <v>100</v>
       </c>
@@ -2042,7 +2258,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C11" s="7"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -2051,7 +2267,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C12" s="7"/>
       <c r="E12" s="3" t="s">
         <v>6</v>
@@ -2072,7 +2288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="s">
         <v>3</v>
       </c>
@@ -2083,19 +2299,19 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C14" s="7"/>
       <c r="M14" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="C16" s="33">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C16" s="32">
         <f>SUM(C4:C15)</f>
         <v>1224</v>
       </c>
@@ -2108,9 +2324,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:9" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <f>ROWS(C3:C16)</f>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2123,22 +2345,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF8DED8-99C4-43E0-BB50-67E4C90943A3}">
   <dimension ref="B1:T24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.26953125" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" customWidth="1"/>
-    <col min="13" max="13" width="21.26953125" customWidth="1"/>
-    <col min="14" max="14" width="10.453125" customWidth="1"/>
-    <col min="16" max="16" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.6328125" customWidth="1"/>
-    <col min="20" max="20" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="13" max="13" width="21.21875" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" customWidth="1"/>
+    <col min="16" max="16" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" customWidth="1"/>
+    <col min="20" max="20" width="3.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J1" s="10" t="s">
         <v>11</v>
       </c>
@@ -2148,21 +2370,21 @@
       <c r="L1" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="60"/>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B2" s="56"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
       <c r="J2" s="9">
         <v>100</v>
       </c>
@@ -2178,21 +2400,17 @@
         <f>IF(J2&gt;74,"Disctinction",IF(J2&gt;59,"First class",IF(J2&gt;34,"Pass","Fail")))</f>
         <v>Disctinction</v>
       </c>
-      <c r="N2" s="17"/>
+      <c r="N2" s="16"/>
       <c r="O2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="63" t="s">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="59"/>
+      <c r="F3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="62"/>
-      <c r="H3" s="64"/>
+      <c r="H3" s="60"/>
       <c r="J3" s="9">
         <v>6</v>
       </c>
@@ -2208,19 +2426,14 @@
         <f t="shared" ref="M3:M16" si="2">IF(J3&gt;74,"Disctinction",IF(J3&gt;59,"First class",IF(J3&gt;34,"Pass","Fail")))</f>
         <v>Fail</v>
       </c>
-      <c r="N3" s="17"/>
+      <c r="N3" s="16"/>
       <c r="O3" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="61"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="64"/>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B4" s="59"/>
+      <c r="H4" s="60"/>
       <c r="J4" s="9">
         <v>82</v>
       </c>
@@ -2236,7 +2449,7 @@
         <f t="shared" si="2"/>
         <v>Disctinction</v>
       </c>
-      <c r="N4" s="17"/>
+      <c r="N4" s="16"/>
       <c r="O4" s="3" t="s">
         <v>20</v>
       </c>
@@ -2253,22 +2466,20 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="61"/>
-      <c r="C5" s="65">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B5" s="59"/>
+      <c r="C5" s="12">
         <v>10</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="66" t="str">
+      <c r="F5" s="1" t="str">
         <f>IF(C5=10,"Ten","Not ten")</f>
         <v>Ten</v>
       </c>
-      <c r="G5" s="62" t="str">
+      <c r="G5" t="str">
         <f>IF(C5&lt;&gt;10,"Not ten","Ten")</f>
         <v>Ten</v>
       </c>
-      <c r="H5" s="64"/>
+      <c r="H5" s="60"/>
       <c r="J5" s="9">
         <v>37</v>
       </c>
@@ -2284,7 +2495,7 @@
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="N5" s="17"/>
+      <c r="N5" s="16"/>
       <c r="O5" s="3" t="s">
         <v>21</v>
       </c>
@@ -2301,16 +2512,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62" t="s">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="59"/>
+      <c r="G6" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="64"/>
+      <c r="H6" s="60"/>
       <c r="J6" s="9">
         <v>89</v>
       </c>
@@ -2326,7 +2533,7 @@
         <f t="shared" si="2"/>
         <v>Disctinction</v>
       </c>
-      <c r="N6" s="17"/>
+      <c r="N6" s="16"/>
       <c r="O6" s="3" t="s">
         <v>22</v>
       </c>
@@ -2343,16 +2550,13 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="67" t="s">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B7" s="59"/>
+      <c r="F7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="61"/>
       <c r="J7" s="9">
         <v>44</v>
       </c>
@@ -2368,7 +2572,7 @@
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="16"/>
       <c r="O7" s="3" t="s">
         <v>23</v>
       </c>
@@ -2385,14 +2589,14 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="69"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="71"/>
+    <row r="8" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
       <c r="J8" s="9">
         <v>8</v>
       </c>
@@ -2408,7 +2612,7 @@
         <f t="shared" si="2"/>
         <v>Fail</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="16"/>
       <c r="O8" s="3" t="s">
         <v>24</v>
       </c>
@@ -2425,11 +2629,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B9" s="72" t="s">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="60"/>
+      <c r="C9" s="58"/>
       <c r="J9" s="9">
         <v>36</v>
       </c>
@@ -2445,7 +2649,7 @@
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="16"/>
       <c r="R9" s="12">
         <v>123</v>
       </c>
@@ -2456,9 +2660,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="61"/>
-      <c r="C10" s="64"/>
+    <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="59"/>
+      <c r="C10" s="60"/>
       <c r="J10" s="9">
         <v>85</v>
       </c>
@@ -2474,7 +2678,7 @@
         <f t="shared" si="2"/>
         <v>Disctinction</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="16"/>
       <c r="R10" s="12">
         <v>123</v>
       </c>
@@ -2485,15 +2689,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="73" t="s">
+    <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="F11" s="41" t="s">
+      <c r="C11" s="64"/>
+      <c r="F11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="42" t="s">
+      <c r="G11" s="40" t="s">
         <v>14</v>
       </c>
       <c r="J11" s="9">
@@ -2511,7 +2715,7 @@
         <f t="shared" si="2"/>
         <v>First class</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="16"/>
       <c r="R11" s="12">
         <v>123</v>
       </c>
@@ -2522,11 +2726,11 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F12" s="43" t="s">
+    <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="42" t="s">
         <v>16</v>
       </c>
       <c r="J12" s="9">
@@ -2544,7 +2748,7 @@
         <f t="shared" si="2"/>
         <v>Fail</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="16"/>
       <c r="P12" t="s">
         <v>80</v>
       </c>
@@ -2558,7 +2762,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J13" s="9">
         <v>13</v>
       </c>
@@ -2574,7 +2778,7 @@
         <f t="shared" si="2"/>
         <v>Fail</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="16"/>
       <c r="R13" s="12">
         <v>123</v>
       </c>
@@ -2585,7 +2789,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>100</v>
       </c>
@@ -2595,10 +2799,10 @@
       <c r="D14" s="4">
         <v>100</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="44" t="s">
         <v>14</v>
       </c>
       <c r="J14" s="9">
@@ -2616,7 +2820,7 @@
         <f t="shared" si="2"/>
         <v>Pass</v>
       </c>
-      <c r="N14" s="17"/>
+      <c r="N14" s="16"/>
       <c r="P14" t="s">
         <v>81</v>
       </c>
@@ -2630,7 +2834,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>100</v>
       </c>
@@ -2640,10 +2844,10 @@
       <c r="D15" s="4">
         <v>100</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="34" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="9">
@@ -2661,7 +2865,7 @@
         <f t="shared" si="2"/>
         <v>Fail</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="16"/>
       <c r="R15" s="12">
         <v>123</v>
       </c>
@@ -2672,7 +2876,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>100</v>
       </c>
@@ -2682,10 +2886,10 @@
       <c r="D16" s="4">
         <v>100</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="38" t="s">
+      <c r="G16" s="36" t="s">
         <v>57</v>
       </c>
       <c r="J16" s="9">
@@ -2703,7 +2907,7 @@
         <f t="shared" si="2"/>
         <v>Disctinction</v>
       </c>
-      <c r="N16" s="17"/>
+      <c r="N16" s="16"/>
       <c r="R16" s="12">
         <v>123</v>
       </c>
@@ -2714,7 +2918,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="4">
         <v>100</v>
       </c>
@@ -2724,10 +2928,10 @@
       <c r="D17" s="4">
         <v>100</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="38" t="s">
         <v>59</v>
       </c>
       <c r="R17" s="12">
@@ -2740,7 +2944,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="4">
         <v>100</v>
       </c>
@@ -2754,7 +2958,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="4">
         <v>100</v>
       </c>
@@ -2769,7 +2973,7 @@
       </c>
       <c r="M19" s="14"/>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="4">
         <v>100</v>
       </c>
@@ -2783,7 +2987,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>100</v>
       </c>
@@ -2794,7 +2998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4">
         <v>100</v>
       </c>
@@ -2804,8 +3008,12 @@
       <c r="D22" s="4">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="G22" t="str">
+        <f>IF(C5=10,"yes","no")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="4">
         <v>100</v>
       </c>
@@ -2816,7 +3024,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="4">
         <v>100</v>
       </c>
@@ -2836,342 +3044,349 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E44FD8F-90E3-43B4-A887-F4067DB35150}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="53" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="51">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="49">
         <v>1001</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="54">
         <v>92</v>
       </c>
       <c r="F2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="51">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="49">
         <v>1002</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="54">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="51">
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="49">
         <v>1003</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="54">
         <v>58</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="28" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="51">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="49">
         <v>1004</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="54">
         <v>81</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="19">
         <v>1006</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="23"/>
-      <c r="L5" t="str">
+      <c r="J5" s="22"/>
+      <c r="L5" s="77" t="str">
         <f>A1</f>
         <v>Emp ID</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M5" s="77" t="str">
         <f t="shared" ref="M5:N15" si="0">B1</f>
         <v>Emp Name</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N5" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Mark</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="51">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="49">
         <v>1005</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="54">
         <v>63</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <v>1009</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="24"/>
-      <c r="L6">
+      <c r="I6" s="15"/>
+      <c r="J6" s="23"/>
+      <c r="L6" s="75">
         <f t="shared" ref="L6:L15" si="1">A2</f>
         <v>1001</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M6" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme1</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="75">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="51">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="49">
         <v>1006</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="54">
         <v>45</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <v>1007</v>
       </c>
       <c r="I7" s="13"/>
-      <c r="J7" s="25"/>
-      <c r="L7">
+      <c r="J7" s="24"/>
+      <c r="L7" s="75">
         <f t="shared" si="1"/>
         <v>1002</v>
       </c>
-      <c r="M7" t="str">
+      <c r="M7" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme2</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="75">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="51">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="49">
         <v>1007</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="54">
         <v>96</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <v>1005</v>
       </c>
       <c r="I8" s="13"/>
-      <c r="J8" s="25"/>
-      <c r="L8">
+      <c r="J8" s="24"/>
+      <c r="L8" s="75">
         <f t="shared" si="1"/>
         <v>1003</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M8" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme3</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="75">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="51">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="49">
         <v>1008</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="54">
         <v>17</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="19">
         <v>1011</v>
       </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="25"/>
-      <c r="L9">
+      <c r="J9" s="24"/>
+      <c r="L9" s="75">
         <f t="shared" si="1"/>
         <v>1004</v>
       </c>
-      <c r="M9" t="str">
+      <c r="M9" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme4</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="75">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="51">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="49">
         <v>1009</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="54">
         <v>92</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <v>1008</v>
       </c>
       <c r="I10" s="13"/>
-      <c r="J10" s="25"/>
-      <c r="L10">
+      <c r="J10" s="24"/>
+      <c r="L10" s="75">
         <f t="shared" si="1"/>
         <v>1005</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M10" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme5</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="75">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="51">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="49">
         <v>1010</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="54">
         <v>46</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="19">
         <v>1010</v>
       </c>
       <c r="I11" s="13"/>
-      <c r="J11" s="23"/>
-      <c r="L11">
+      <c r="J11" s="22"/>
+      <c r="L11" s="75">
         <f t="shared" si="1"/>
         <v>1006</v>
       </c>
-      <c r="M11" t="str">
+      <c r="M11" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme6</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="75">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="52"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="54"/>
-      <c r="H12" s="20">
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="H12" s="19">
         <v>1001</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="25"/>
-      <c r="L12">
+      <c r="J12" s="24"/>
+      <c r="L12" s="75">
         <f t="shared" si="1"/>
         <v>1007</v>
       </c>
-      <c r="M12" t="str">
+      <c r="M12" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme7</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="75">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H13" s="22">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H13" s="21">
         <v>1002</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="26"/>
-      <c r="L13">
+      <c r="J13" s="25"/>
+      <c r="L13" s="75">
         <f t="shared" si="1"/>
         <v>1008</v>
       </c>
-      <c r="M13" t="str">
+      <c r="M13" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme8</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="75">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H14" s="20">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H14" s="19">
         <v>1003</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="25"/>
-      <c r="L14">
+      <c r="J14" s="24"/>
+      <c r="L14" s="75">
         <f t="shared" si="1"/>
         <v>1009</v>
       </c>
-      <c r="M14" t="str">
+      <c r="M14" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Nme9</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="75">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H15" s="30">
+    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H15" s="29">
         <v>1004</v>
       </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="32"/>
-      <c r="L15">
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="L15" s="76">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M15" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Nme10</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="76">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -3190,13 +3405,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451686C8-E6DE-48A3-BFFB-7792A1CD1DDB}">
-  <dimension ref="B4:M13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B4:N16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -3209,7 +3424,7 @@
       <c r="J4">
         <v>100</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
@@ -3218,12 +3433,15 @@
       <c r="M4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="F5" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
@@ -3236,7 +3454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
@@ -3253,7 +3471,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J7">
         <v>100</v>
       </c>
@@ -3267,7 +3485,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J8">
         <v>100</v>
       </c>
@@ -3281,7 +3499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="E9" s="1"/>
       <c r="I9" s="12"/>
       <c r="J9">
@@ -3297,7 +3515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="J10">
         <v>100</v>
@@ -3312,7 +3530,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J11">
         <v>100</v>
       </c>
@@ -3326,7 +3544,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J12">
         <v>100</v>
       </c>
@@ -3340,7 +3558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="G13" s="1"/>
       <c r="J13">
         <v>100</v>
@@ -3352,6 +3570,21 @@
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J16">
         <v>100</v>
       </c>
     </row>
